--- a/reports/telegram/aegis_india_2026-09-01.xlsx
+++ b/reports/telegram/aegis_india_2026-09-01.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -489,9 +489,11 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -551,17 +553,27 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>Dynamic Stop</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Engine Verdict</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Would-Have-Exited-On</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>As-Of</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Provenance</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -598,19 +610,27 @@
       <c r="H5" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="n">
+        <v>545.1072</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -647,19 +667,27 @@
       <c r="H6" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="n">
+        <v>11017</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -696,19 +724,27 @@
       <c r="H7" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="n">
+        <v>399.7929</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -745,19 +781,27 @@
       <c r="H8" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="n">
+        <v>5402.5</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -794,19 +838,27 @@
       <c r="H9" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="n">
+        <v>2619.7713</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -843,19 +895,27 @@
       <c r="H10" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="n">
+        <v>636.7429</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -892,19 +952,27 @@
       <c r="H11" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -941,19 +1009,27 @@
       <c r="H12" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -990,19 +1066,27 @@
       <c r="H13" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="n">
+        <v>109.8471</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1118,38 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Dynamic Stop = today's stop level from the coded exit engine (dynamic_risk_v2 ATR-based, else recommendation entry_zone.stop_loss, else entry × 0.94).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Engine Verdict = what the coded lifecycle engine (evaluate_position) says today. HOLD if no trigger. EXIT_STOP / EXIT_TARGET / EXIT_HORIZON if triggered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Would-Have-Exited-On = if the engine says exit today, this is the first date the position crossed the trigger. Positions are NOT retroactively closed in the current release · this is audit-only until the wiring is enforced.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
+  <mergeCells count="9">
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A16:M16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
